--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1280.6</v>
+        <v>57567.36</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>550.6065</v>
+        <v>24751.65</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1022.0808</v>
+        <v>45946.04</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>664.02</v>
+        <v>29849.98</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>281.0218</v>
+        <v>12632.89</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>811.89</v>
+        <v>36497.24</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>548.1347</v>
+        <v>24640.53</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1238.3136</v>
+        <v>55666.44</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1100.8918</v>
+        <v>49488.86</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6566.4</v>
+        <v>295182.2</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1662.5</v>
+        <v>74735.08</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>615.5424</v>
+        <v>27670.74</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>781.85</v>
+        <v>35146.84</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>372</v>
+        <v>16722.68</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>511.5</v>
+        <v>22993.68</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1322.88</v>
+        <v>59467.99</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>854.0665</v>
+        <v>38393.22</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>809.1</v>
+        <v>36371.82</v>
       </c>
     </row>
     <row r="20">
@@ -1663,17 +1663,17 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>465</v>
+        <v>20903.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>552975-23-CM26</t>
+          <t>1602-4-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,28 +1713,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>VIA 56 S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.707.293-7</t>
+          <t>96.928.990-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>176.0304</v>
+        <v>17783.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1602-4-CM26</t>
+          <t>552975-23-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,22 +1774,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>VIA 56 S A</t>
+          <t>ADOLFO IGNACIO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.928.990-3</t>
+          <t>76.707.293-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>395.5961</v>
+        <v>7913.17</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>454.1748</v>
+        <v>20416.71</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>482.4872</v>
+        <v>21689.45</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1101.6209</v>
+        <v>49521.64</v>
       </c>
     </row>
     <row r="26">
@@ -2029,17 +2029,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1167.48</v>
+        <v>52482.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1233615-13-CM26</t>
+          <t>1233616-170-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,48 +2059,48 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>530.1</v>
+        <v>15156.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1233616-170-CM26</t>
+          <t>5403-3-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,53 +2115,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>337.1529</v>
+        <v>580026</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5403-3-CM26</t>
+          <t>411-22-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,43 +2186,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12902.82</v>
+        <v>8407.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>411-22-CM26</t>
+          <t>1389585-15-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,47 +2237,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>70.882.100-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>187.0323</v>
+        <v>8361.34</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>569.16</v>
+        <v>25585.69</v>
       </c>
     </row>
     <row r="32">
@@ -2395,17 +2395,17 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1202.8</v>
+        <v>54069.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1389585-15-CM26</t>
+          <t>5155-10-SE26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70.882.100-4</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>Servicio Electoral</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2445,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>186</v>
+        <v>1798.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5155-10-SE26</t>
+          <t>1562-19-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,47 +2495,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>39.9999546222</v>
+        <v>66626.96000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1562-19-CM26</t>
+          <t>1057506-2288-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,43 +2556,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1482.133</v>
+        <v>16049.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057506-2288-CM25</t>
+          <t>1186229-10-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,43 +2617,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Pragma Informatica S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>357.027</v>
+        <v>654773.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1186229-10-CM26</t>
+          <t>4192-3-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,53 +2668,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>14565.6008</v>
+        <v>15374.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4192-3-CM26</t>
+          <t>1351461-5-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2734,48 +2734,48 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>60.801.000-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>Asimov Consultores SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>342</v>
+        <v>51350.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1351461-5-CM26</t>
+          <t>1075952-9-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.801.000-9</t>
+          <t>62.000.580-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE HACIENDA</t>
+          <t>Superintendencia de Educación Superior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,28 +2815,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1142.3032</v>
+        <v>11315.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1075952-9-CM26</t>
+          <t>4301-59-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2856,48 +2856,48 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.580-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Superintendencia de Educación Superior</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>251.7247</v>
+        <v>25623.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4301-59-CM26</t>
+          <t>5413-88-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,53 +2912,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>570</v>
+        <v>36524</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5413-88-CM26</t>
+          <t>4754-1-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,43 +2983,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>MCL CONSULTING</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.314.701-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>812.4852</v>
+        <v>22959.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4754-1-CM26</t>
+          <t>584264-27-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3059,22 +3059,22 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MCL CONSULTING</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.314.701-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>510.7368</v>
+        <v>31260.61</v>
       </c>
     </row>
     <row r="44">
@@ -3131,17 +3131,17 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>669.7674</v>
+        <v>30108.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>584264-27-CM26</t>
+          <t>635-84-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3161,103 +3161,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>RAYEN SALUD SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>695.4</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>635-84-CM26</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>61.606.000-7</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>RAYEN SALUD SPA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>77.917.240-6</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>485.9404</v>
+        <v>21844.69</v>
       </c>
     </row>
   </sheetData>
